--- a/Config/Sfx.xlsx
+++ b/Config/Sfx.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\zizouqi\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4806B92-4DDB-48A5-866E-9D28DD10BA0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33ED996F-3203-439F-933E-4B18AA1C8627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21600" yWindow="390" windowWidth="21810" windowHeight="23430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="100" yWindow="0" windowWidth="21850" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
   <si>
     <t>#</t>
   </si>
@@ -157,6 +157,14 @@
   </si>
   <si>
     <t>0.3,0.3,0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆炸blue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -482,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="17.83203125" customWidth="1"/>
@@ -663,6 +671,29 @@
         <v>33</v>
       </c>
     </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8">
+        <v>3304</v>
+      </c>
+      <c r="E8">
+        <v>1000</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="J8" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
